--- a/lorenzo-playwright-kdf/excelFramework/testcases/MSI/LSTP_MSI_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/MSI/LSTP_MSI_WF001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smani57\ORBIS PAS UKI-LZO 1\ORBIS PAS UKI-LZO\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\MSI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\MSI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14966499-DFD9-4A31-AC6A-57810B9D84DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BAA268-A065-4F37-B015-9DBC5A91F5B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{702FC42C-4FAC-40FC-8DEB-CEC87A00E4C0}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{702FC42C-4FAC-40FC-8DEB-CEC87A00E4C0}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -1386,7 +1386,7 @@
         <v>261</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>195</v>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/MSI/LSTP_MSI_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/MSI/LSTP_MSI_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\MSI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BAA268-A065-4F37-B015-9DBC5A91F5B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{751760E1-45F6-43D4-86C2-523A3A93D60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{702FC42C-4FAC-40FC-8DEB-CEC87A00E4C0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="266">
   <si>
     <t>StepNo</t>
   </si>
@@ -834,6 +834,9 @@
   </si>
   <si>
     <t>pageRegRegistrationTemporary</t>
+  </si>
+  <si>
+    <t>exists</t>
   </si>
 </sst>
 </file>
@@ -1561,6 +1564,9 @@
       <c r="F11" t="s">
         <v>31</v>
       </c>
+      <c r="G11" t="s">
+        <v>265</v>
+      </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/MSI/LSTP_MSI_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/MSI/LSTP_MSI_WF001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\MSI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{751760E1-45F6-43D4-86C2-523A3A93D60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1853219-0736-46CB-B646-CE81098F8647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{702FC42C-4FAC-40FC-8DEB-CEC87A00E4C0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{702FC42C-4FAC-40FC-8DEB-CEC87A00E4C0}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="266">
   <si>
     <t>StepNo</t>
   </si>
@@ -1638,6 +1638,9 @@
       <c r="F15" t="s">
         <v>31</v>
       </c>
+      <c r="G15" t="s">
+        <v>265</v>
+      </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
@@ -1771,6 +1774,9 @@
       <c r="F23" t="s">
         <v>31</v>
       </c>
+      <c r="G23" t="s">
+        <v>265</v>
+      </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
@@ -2055,6 +2061,9 @@
       <c r="F39" t="s">
         <v>31</v>
       </c>
+      <c r="G39" t="s">
+        <v>265</v>
+      </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
@@ -2395,6 +2404,9 @@
       <c r="F59" t="s">
         <v>31</v>
       </c>
+      <c r="G59" t="s">
+        <v>265</v>
+      </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
@@ -2638,6 +2650,9 @@
       <c r="F74" t="s">
         <v>31</v>
       </c>
+      <c r="G74" t="s">
+        <v>265</v>
+      </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
@@ -2689,6 +2704,9 @@
       <c r="F77" t="s">
         <v>31</v>
       </c>
+      <c r="G77" t="s">
+        <v>265</v>
+      </c>
       <c r="J77" t="b">
         <v>1</v>
       </c>
@@ -2757,6 +2775,9 @@
       <c r="F81" t="s">
         <v>31</v>
       </c>
+      <c r="G81" t="s">
+        <v>265</v>
+      </c>
       <c r="J81" t="b">
         <v>1</v>
       </c>
@@ -2952,6 +2973,9 @@
       <c r="F93" t="s">
         <v>31</v>
       </c>
+      <c r="G93" t="s">
+        <v>265</v>
+      </c>
       <c r="J93" t="b">
         <v>1</v>
       </c>
@@ -3003,6 +3027,9 @@
       <c r="F96" t="s">
         <v>31</v>
       </c>
+      <c r="G96" t="s">
+        <v>265</v>
+      </c>
       <c r="J96" t="b">
         <v>1</v>
       </c>
@@ -3071,6 +3098,9 @@
       <c r="F100" t="s">
         <v>31</v>
       </c>
+      <c r="G100" t="s">
+        <v>265</v>
+      </c>
       <c r="J100" t="b">
         <v>1</v>
       </c>
@@ -3152,6 +3182,9 @@
       </c>
       <c r="F105" t="s">
         <v>31</v>
+      </c>
+      <c r="G105" t="s">
+        <v>265</v>
       </c>
       <c r="J105" t="b">
         <v>1</v>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/MSI/LSTP_MSI_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/MSI/LSTP_MSI_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\MSI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1853219-0736-46CB-B646-CE81098F8647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8954A172-4F64-42F7-9779-62145ECECA97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{702FC42C-4FAC-40FC-8DEB-CEC87A00E4C0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="267">
   <si>
     <t>StepNo</t>
   </si>
@@ -837,6 +837,9 @@
   </si>
   <si>
     <t>exists</t>
+  </si>
+  <si>
+    <t>launchRegistration</t>
   </si>
 </sst>
 </file>
@@ -1500,7 +1503,7 @@
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1531,7 +1534,7 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1585,7 +1588,7 @@
         <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1659,7 +1662,7 @@
         <v>42</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>266</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1741,7 +1744,7 @@
         <v>49</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1795,7 +1798,7 @@
         <v>55</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1906,7 +1909,7 @@
         <v>69</v>
       </c>
       <c r="F30" t="s">
-        <v>15</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -2028,7 +2031,7 @@
         <v>83</v>
       </c>
       <c r="F37" t="s">
-        <v>15</v>
+        <v>266</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -2102,7 +2105,7 @@
         <v>33</v>
       </c>
       <c r="F41" t="s">
-        <v>15</v>
+        <v>266</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">

--- a/lorenzo-playwright-kdf/excelFramework/testcases/MSI/LSTP_MSI_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/MSI/LSTP_MSI_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\MSI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8954A172-4F64-42F7-9779-62145ECECA97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B792D8A-488B-47EE-92CE-A14093A202D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{702FC42C-4FAC-40FC-8DEB-CEC87A00E4C0}"/>
   </bookViews>
@@ -2079,7 +2079,7 @@
         <v>87</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D40" t="s">
         <v>88</v>
